--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>45596</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>46239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45337</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45884</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44747</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>46010</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>46188</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>46122</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>44951</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45476</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>44602</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46122</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>46080</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45531</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>46071</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>46141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45590</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>46036</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>46191</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45103</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>44547</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>45068</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>45798</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>45930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>44942</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45763</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44874</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>46191</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>46122</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>46122</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>45918</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45733</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>45602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45460</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45390</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45685</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>44701</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>45481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>45763</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45804</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44468</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>44572</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44881</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44586</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>44603</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>44741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>44725</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44809</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>44462</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44692</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44551</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44837</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44860</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>44677</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44819</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>44722</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44846</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>44624</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44495</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44518</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44565</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44617</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44645</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44518</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44830</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44606</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>44740</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>44573</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44474</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>44571</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44809</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>44503</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44799</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>44834</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>44574</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44574</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44525</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>44608</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>44830</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44526</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44528</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44501</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44518</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44496</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44484</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44809</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44984</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45187</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44615</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45387</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44879</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45747</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45001</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45079</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45454</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45183</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44606</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45114</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>45343</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45597</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44566</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45302</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44992</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44734</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44748</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45215</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>44952</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45173</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>44935</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45644</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44750</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45440</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45540</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45111</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45546</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45429</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44459</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45279</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45202</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44575</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44967</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44967</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45401</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44776</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44942</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44935</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44865</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44890</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44914</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45470</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44645</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45237</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44830</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45187</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44830</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45343</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44628</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44487</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44967</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>44967</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45695</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>44865</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44911</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45954</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44931</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45889</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>45099</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>45335</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45439</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45215</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45215</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44592</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45575</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44881</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45898</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45880</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45839</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45621</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45659</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>45593</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>44776</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>44951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17452,7 +17452,7 @@
         <v>45351</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>45923</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>45114</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>46141</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>45460</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>46142</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45930</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45930</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>46142</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45930</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45069</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>46142</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45930</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45930</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45615</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45092</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45243</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45484</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44539</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45939</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45938</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45938</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44748</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>44942</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>45425</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>44725</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45945</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45603</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>45946</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45427</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>44958</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45099</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>45624</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44516</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>45964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45965</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45964</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45812</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45205</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44676</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>44613</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45294</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45161</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>45029</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45614</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>45589</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45484</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>46158</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46160</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45266</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>46160</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46160</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>46160</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>46163</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45602</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45614</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45266</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45224</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44984</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45428</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45562</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44942</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44853</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45279</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45279</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>46003</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44942</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45998</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46003</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>44935</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>46167</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>44819</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45439</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45187</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45562</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>44503</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45034</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44830</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>46034</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45061</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>46174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46174</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>46174</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>46174</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45183</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45526</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>46001</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46055</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45351</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45473</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>45302</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45043</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>46058</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45427</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>45440</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>46061</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>46064</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>44637</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46064</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44998</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>46066</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45685</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>46066</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>46066</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>46066</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>46066</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>46066</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>46069</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46069</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>46066</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44608</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44608</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>46073</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46077</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>46080</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>46080</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45378</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44725</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>44987</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46188</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>46188</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45377</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>46091</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>46091</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>46091</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45377</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>46092</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>46190</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>46092</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>46092</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>46094</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>46094</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>46190</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45793</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>46094</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>46094</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>46190</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44742</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>46191</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45243</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>46104</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>46198</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>46100</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>46106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>46198</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>46198</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>46198</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46105</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>46105</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>46105</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45243</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45273</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>44804</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>45237</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46202</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>46122</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44516</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>46122</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>46199</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>46243</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44782</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>44573</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>46066</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>46132</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>46132</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>46204</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>44999</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45180</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44894</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45476</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>44893</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45030</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44641</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>44494</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44930</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>46206</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44679</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>44776</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45229</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>46255</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>46255</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>46255</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46255</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45204</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45222</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44725</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44819</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44830</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>46218</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>46218</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46218</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>46259</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>44830</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>45329</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>44931</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45343</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45091</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>44907</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>46273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45615</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45781</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45708</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45632</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44903</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45469</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45589</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>46281</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45604</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45222</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>46281</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45666</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45547</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45629</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45644</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45630</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45689</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>45798</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45803</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>45112</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>44901</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45831</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45839</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45817</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45316</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45575</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45726</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45805</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>45798</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45747</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>45575</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45526</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45205</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>45474</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>45475</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45763</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45786</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45796</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>46071</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>46077</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>46104</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -622,13 +622,13 @@
         <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -643,36 +643,43 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="T2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Grönhjon
 Orange taggsvamp
 Rödvingetrast
+Sotvaxskivling
 Svart skogssnigel
+Svartvit taggsvamp
 Tallticka
 Talltita
+Ullticka
 Älg
 Björksplintborre
 Grönpyrola
 Rödgul trumpetsvamp
+Vågbandad barkbock
 Bergsslok
 Liljekonvalj
 Linnea
+Mattlummer
 Spillkråka
 Tofsmes
 Vanlig groda
@@ -736,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1120,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1232,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1359,7 @@
         <v>45897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1467,7 +1474,7 @@
         <v>45596</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1587,7 +1594,7 @@
         <v>46239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1706,7 +1713,7 @@
         <v>45337</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1824,7 @@
         <v>45884</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1940,7 @@
         <v>46122</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2059,7 @@
         <v>46010</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2171,7 +2178,7 @@
         <v>46188</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2290,7 +2297,7 @@
         <v>44747</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2404,7 +2411,7 @@
         <v>44951</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2526,7 +2533,7 @@
         <v>45476</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2644,7 +2651,7 @@
         <v>44602</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2756,7 +2763,7 @@
         <v>46122</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2873,7 +2880,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2986,7 +2993,7 @@
         <v>46080</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3102,7 +3109,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3214,7 +3221,7 @@
         <v>45671</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3330,7 +3337,7 @@
         <v>45531</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3437,7 +3444,7 @@
         <v>46071</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3544,7 +3551,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3650,7 +3657,7 @@
         <v>45958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3756,7 +3763,7 @@
         <v>45103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3871,7 +3878,7 @@
         <v>46141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3977,7 +3984,7 @@
         <v>45918</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4090,7 @@
         <v>46191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4194,7 +4201,7 @@
         <v>45590</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4300,7 +4307,7 @@
         <v>45044</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4406,7 +4413,7 @@
         <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4521,7 +4528,7 @@
         <v>44544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4631,7 +4638,7 @@
         <v>44547</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4741,7 +4748,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4855,7 +4862,7 @@
         <v>44874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4965,7 +4972,7 @@
         <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5070,7 +5077,7 @@
         <v>46122</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5184,7 +5191,7 @@
         <v>46122</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5294,7 +5301,7 @@
         <v>44942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5403,7 +5410,7 @@
         <v>45798</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5508,7 +5515,7 @@
         <v>45918</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,7 +5620,7 @@
         <v>46191</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5727,7 +5734,7 @@
         <v>45763</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5837,7 +5844,7 @@
         <v>45068</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5942,7 +5949,7 @@
         <v>45733</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6047,7 +6054,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6159,7 @@
         <v>45602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6257,7 +6264,7 @@
         <v>45390</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6362,7 +6369,7 @@
         <v>44701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6472,7 +6479,7 @@
         <v>45685</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6586,7 +6593,7 @@
         <v>45481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6696,7 +6703,7 @@
         <v>45763</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6806,7 +6813,7 @@
         <v>45804</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6923,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6989,7 +6996,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7062,7 +7069,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7135,7 +7142,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7208,7 +7215,7 @@
         <v>44468</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7281,7 +7288,7 @@
         <v>44586</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7354,7 +7361,7 @@
         <v>44603</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7432,7 +7439,7 @@
         <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7505,7 +7512,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7578,7 +7585,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7656,7 +7663,7 @@
         <v>44741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7729,7 +7736,7 @@
         <v>44628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7807,7 +7814,7 @@
         <v>44692</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7885,7 +7892,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7958,7 +7965,7 @@
         <v>44837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8031,7 +8038,7 @@
         <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8104,7 +8111,7 @@
         <v>44677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8177,7 +8184,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8255,7 +8262,7 @@
         <v>44819</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8328,7 +8335,7 @@
         <v>44860</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8406,7 +8413,7 @@
         <v>44722</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8479,7 +8486,7 @@
         <v>44846</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8552,7 +8559,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8625,7 +8632,7 @@
         <v>44624</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8698,7 +8705,7 @@
         <v>44495</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8771,7 +8778,7 @@
         <v>44518</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8844,7 +8851,7 @@
         <v>44565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8917,7 +8924,7 @@
         <v>44518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8990,7 +8997,7 @@
         <v>44617</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9063,7 +9070,7 @@
         <v>44645</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9136,7 +9143,7 @@
         <v>44830</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9214,7 +9221,7 @@
         <v>44606</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9287,7 +9294,7 @@
         <v>44740</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9360,7 +9367,7 @@
         <v>44573</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9433,7 +9440,7 @@
         <v>44474</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9506,7 +9513,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9579,7 +9586,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9657,7 +9664,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9730,7 +9737,7 @@
         <v>44799</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9803,7 +9810,7 @@
         <v>44834</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9876,7 +9883,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9949,7 +9956,7 @@
         <v>44574</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10022,7 +10029,7 @@
         <v>44525</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10095,7 +10102,7 @@
         <v>44608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10168,7 +10175,7 @@
         <v>44830</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10246,7 +10253,7 @@
         <v>44749</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10319,7 +10326,7 @@
         <v>44882</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10397,7 +10404,7 @@
         <v>44526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10470,7 +10477,7 @@
         <v>44796</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10548,7 +10555,7 @@
         <v>44528</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10621,7 +10628,7 @@
         <v>44501</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10694,7 +10701,7 @@
         <v>44518</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10767,7 +10774,7 @@
         <v>44496</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10840,7 +10847,7 @@
         <v>44484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10913,7 +10920,7 @@
         <v>44809</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10991,7 +10998,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11069,7 +11076,7 @@
         <v>45215</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11142,7 +11149,7 @@
         <v>45335</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11220,7 +11227,7 @@
         <v>45377</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11293,7 +11300,7 @@
         <v>45378</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11366,7 +11373,7 @@
         <v>44776</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11439,7 +11446,7 @@
         <v>45069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11512,7 +11519,7 @@
         <v>45439</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11585,7 +11592,7 @@
         <v>45440</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11658,7 +11665,7 @@
         <v>44830</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11736,7 +11743,7 @@
         <v>45427</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11809,7 +11816,7 @@
         <v>45302</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11887,7 +11894,7 @@
         <v>45387</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11960,7 +11967,7 @@
         <v>44853</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12038,7 +12045,7 @@
         <v>45666</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12111,7 +12118,7 @@
         <v>45526</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12184,7 +12191,7 @@
         <v>45470</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12262,7 +12269,7 @@
         <v>45279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12335,7 +12342,7 @@
         <v>45279</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12408,7 +12415,7 @@
         <v>44894</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12486,7 +12493,7 @@
         <v>45629</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12559,7 +12566,7 @@
         <v>45092</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12637,7 +12644,7 @@
         <v>45644</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12710,7 +12717,7 @@
         <v>45279</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12783,7 +12790,7 @@
         <v>44942</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12856,7 +12863,7 @@
         <v>45630</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12929,7 +12936,7 @@
         <v>45266</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13002,7 +13009,7 @@
         <v>45266</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13075,7 +13082,7 @@
         <v>45266</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13148,7 +13155,7 @@
         <v>45689</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13221,7 +13228,7 @@
         <v>45547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13294,7 +13301,7 @@
         <v>45798</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13372,7 +13379,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13445,7 +13452,7 @@
         <v>45889</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13518,7 +13525,7 @@
         <v>45898</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13591,7 +13598,7 @@
         <v>45898</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13664,7 +13671,7 @@
         <v>46001</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13737,7 +13744,7 @@
         <v>45575</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13810,7 +13817,7 @@
         <v>44953</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13883,7 +13890,7 @@
         <v>46055</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13956,7 +13963,7 @@
         <v>44539</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14029,7 +14036,7 @@
         <v>46058</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14102,7 +14109,7 @@
         <v>45202</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14175,7 +14182,7 @@
         <v>46061</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14248,7 +14255,7 @@
         <v>45803</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14321,7 +14328,7 @@
         <v>45001</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14394,7 +14401,7 @@
         <v>46064</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14467,7 +14474,7 @@
         <v>46064</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14540,7 +14547,7 @@
         <v>46066</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14618,7 +14625,7 @@
         <v>46066</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14696,7 +14703,7 @@
         <v>46066</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14774,7 +14781,7 @@
         <v>46066</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14852,7 +14859,7 @@
         <v>46066</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14930,7 +14937,7 @@
         <v>46066</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15008,7 +15015,7 @@
         <v>45923</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15081,7 +15088,7 @@
         <v>46069</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15154,7 +15161,7 @@
         <v>46069</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15227,7 +15234,7 @@
         <v>46077</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15300,7 +15307,7 @@
         <v>46073</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15373,7 +15380,7 @@
         <v>45930</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15446,7 +15453,7 @@
         <v>45930</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15519,7 +15526,7 @@
         <v>45930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15592,7 +15599,7 @@
         <v>45930</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15665,7 +15672,7 @@
         <v>45930</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15738,7 +15745,7 @@
         <v>45930</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15811,7 +15818,7 @@
         <v>45930</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15884,7 +15891,7 @@
         <v>45930</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15957,7 +15964,7 @@
         <v>46080</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16030,7 +16037,7 @@
         <v>44931</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16108,7 +16115,7 @@
         <v>45440</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16181,7 +16188,7 @@
         <v>45343</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16254,7 +16261,7 @@
         <v>44907</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16327,7 +16334,7 @@
         <v>46091</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16400,7 +16407,7 @@
         <v>46091</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16473,7 +16480,7 @@
         <v>46091</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16546,7 +16553,7 @@
         <v>45938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16624,7 +16631,7 @@
         <v>45938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16702,7 +16709,7 @@
         <v>45229</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16775,7 +16782,7 @@
         <v>46092</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16848,7 +16855,7 @@
         <v>46092</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16921,7 +16928,7 @@
         <v>46092</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16994,7 +17001,7 @@
         <v>45939</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17072,7 +17079,7 @@
         <v>44951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17150,7 +17157,7 @@
         <v>46094</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17228,7 +17235,7 @@
         <v>46094</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17306,7 +17313,7 @@
         <v>46094</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17384,7 +17391,7 @@
         <v>46094</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17462,7 +17469,7 @@
         <v>44911</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17535,7 +17542,7 @@
         <v>46100</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17613,7 +17620,7 @@
         <v>45946</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17686,7 +17693,7 @@
         <v>44679</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17759,7 +17766,7 @@
         <v>45945</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17832,7 +17839,7 @@
         <v>46104</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17905,7 +17912,7 @@
         <v>46105</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17978,7 +17985,7 @@
         <v>46105</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18051,7 +18058,7 @@
         <v>46106</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18124,7 +18131,7 @@
         <v>45607</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18202,7 +18209,7 @@
         <v>45180</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18275,7 +18282,7 @@
         <v>45964</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18353,7 +18360,7 @@
         <v>46122</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18426,7 +18433,7 @@
         <v>46122</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18504,7 +18511,7 @@
         <v>45964</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18577,7 +18584,7 @@
         <v>45965</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18650,7 +18657,7 @@
         <v>44942</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18723,7 +18730,7 @@
         <v>44952</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18796,7 +18803,7 @@
         <v>45644</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18869,7 +18876,7 @@
         <v>44503</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18942,7 +18949,7 @@
         <v>46132</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19020,7 +19027,7 @@
         <v>46132</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19098,7 +19105,7 @@
         <v>45615</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19171,7 +19178,7 @@
         <v>44999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19249,7 +19256,7 @@
         <v>44819</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19322,7 +19329,7 @@
         <v>45614</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19395,7 +19402,7 @@
         <v>45954</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19473,7 +19480,7 @@
         <v>45099</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19546,7 +19553,7 @@
         <v>45161</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19619,7 +19626,7 @@
         <v>44782</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19692,7 +19699,7 @@
         <v>45695</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19765,7 +19772,7 @@
         <v>45114</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19838,7 +19845,7 @@
         <v>45998</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19911,7 +19918,7 @@
         <v>46003</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19984,7 +19991,7 @@
         <v>46003</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20057,7 +20064,7 @@
         <v>45839</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20130,7 +20137,7 @@
         <v>44819</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20203,7 +20210,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20276,7 +20283,7 @@
         <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20349,7 +20356,7 @@
         <v>44901</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20422,7 +20429,7 @@
         <v>45112</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20495,7 +20502,7 @@
         <v>46141</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20568,7 +20575,7 @@
         <v>46142</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20646,7 +20653,7 @@
         <v>44615</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20719,7 +20726,7 @@
         <v>45043</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20797,7 +20804,7 @@
         <v>45243</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20875,7 +20882,7 @@
         <v>45243</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20953,7 +20960,7 @@
         <v>46142</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21031,7 +21038,7 @@
         <v>45831</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21104,7 +21111,7 @@
         <v>46142</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21182,7 +21189,7 @@
         <v>44881</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21255,7 +21262,7 @@
         <v>44890</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21328,7 +21335,7 @@
         <v>44750</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21401,7 +21408,7 @@
         <v>44879</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21479,7 +21486,7 @@
         <v>45812</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21552,7 +21559,7 @@
         <v>45562</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21625,7 +21632,7 @@
         <v>45279</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21698,7 +21705,7 @@
         <v>46160</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21776,7 +21783,7 @@
         <v>46158</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21849,7 +21856,7 @@
         <v>45484</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21922,7 +21929,7 @@
         <v>46160</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22000,7 +22007,7 @@
         <v>46160</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22078,7 +22085,7 @@
         <v>45183</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22151,7 +22158,7 @@
         <v>46160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22229,7 +22236,7 @@
         <v>45839</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22302,7 +22309,7 @@
         <v>44998</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22380,7 +22387,7 @@
         <v>45817</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22453,7 +22460,7 @@
         <v>45316</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22526,7 +22533,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22599,7 +22606,7 @@
         <v>46163</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22677,7 +22684,7 @@
         <v>45575</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22750,7 +22757,7 @@
         <v>45726</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22823,7 +22830,7 @@
         <v>46167</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22901,7 +22908,7 @@
         <v>45805</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22974,7 +22981,7 @@
         <v>45237</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23047,7 +23054,7 @@
         <v>45329</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23120,7 +23127,7 @@
         <v>44676</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23193,7 +23200,7 @@
         <v>45593</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23271,7 +23278,7 @@
         <v>45798</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23349,7 +23356,7 @@
         <v>44628</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23427,7 +23434,7 @@
         <v>45111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23500,7 +23507,7 @@
         <v>46174</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23578,7 +23585,7 @@
         <v>44865</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23651,7 +23658,7 @@
         <v>46174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23729,7 +23736,7 @@
         <v>45069</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23802,7 +23809,7 @@
         <v>45747</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23875,7 +23882,7 @@
         <v>46174</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23953,7 +23960,7 @@
         <v>45029</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24026,7 +24033,7 @@
         <v>46174</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24104,7 +24111,7 @@
         <v>45428</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24177,7 +24184,7 @@
         <v>44516</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24250,7 +24257,7 @@
         <v>44984</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24323,7 +24330,7 @@
         <v>44987</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24401,7 +24408,7 @@
         <v>46188</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24479,7 +24486,7 @@
         <v>45793</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24557,7 +24564,7 @@
         <v>45173</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24630,7 +24637,7 @@
         <v>45575</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24703,7 +24710,7 @@
         <v>46188</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24781,7 +24788,7 @@
         <v>45602</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24854,7 +24861,7 @@
         <v>46190</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24932,7 +24939,7 @@
         <v>46190</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25010,7 +25017,7 @@
         <v>45343</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25083,7 +25090,7 @@
         <v>45484</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25156,7 +25163,7 @@
         <v>46191</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25234,7 +25241,7 @@
         <v>46190</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25307,7 +25314,7 @@
         <v>44606</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25380,7 +25387,7 @@
         <v>45187</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25453,7 +25460,7 @@
         <v>45377</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25526,7 +25533,7 @@
         <v>45439</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25599,7 +25606,7 @@
         <v>46198</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25677,7 +25684,7 @@
         <v>46198</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25755,7 +25762,7 @@
         <v>46199</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25828,7 +25835,7 @@
         <v>46198</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25906,7 +25913,7 @@
         <v>46198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25984,7 +25991,7 @@
         <v>45473</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26057,7 +26064,7 @@
         <v>45187</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26130,7 +26137,7 @@
         <v>44645</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26203,7 +26210,7 @@
         <v>46202</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26276,7 +26283,7 @@
         <v>46066</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26354,7 +26361,7 @@
         <v>45427</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26427,7 +26434,7 @@
         <v>46204</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26505,7 +26512,7 @@
         <v>45351</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26578,7 +26585,7 @@
         <v>45597</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26656,7 +26663,7 @@
         <v>45624</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26729,7 +26736,7 @@
         <v>45183</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26802,7 +26809,7 @@
         <v>45621</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26880,7 +26887,7 @@
         <v>45224</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26953,7 +26960,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27026,7 +27033,7 @@
         <v>44608</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27099,7 +27106,7 @@
         <v>44608</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27172,7 +27179,7 @@
         <v>45685</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27245,7 +27252,7 @@
         <v>45351</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27318,7 +27325,7 @@
         <v>46255</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27396,7 +27403,7 @@
         <v>46255</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27474,7 +27481,7 @@
         <v>46255</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27552,7 +27559,7 @@
         <v>45099</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27625,7 +27632,7 @@
         <v>46255</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27703,7 +27710,7 @@
         <v>45614</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27776,7 +27783,7 @@
         <v>46259</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27849,7 +27856,7 @@
         <v>44748</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27922,7 +27929,7 @@
         <v>44748</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27995,7 +28002,7 @@
         <v>44725</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28068,7 +28075,7 @@
         <v>45237</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28141,7 +28148,7 @@
         <v>44776</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28214,7 +28221,7 @@
         <v>46218</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28292,7 +28299,7 @@
         <v>46218</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28370,7 +28377,7 @@
         <v>46218</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28448,7 +28455,7 @@
         <v>45187</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28521,7 +28528,7 @@
         <v>45302</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28599,7 +28606,7 @@
         <v>44734</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28672,7 +28679,7 @@
         <v>45266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28745,7 +28752,7 @@
         <v>44804</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28818,7 +28825,7 @@
         <v>44725</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28891,7 +28898,7 @@
         <v>44958</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28964,7 +28971,7 @@
         <v>46273</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29037,7 +29044,7 @@
         <v>45273</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29115,7 +29122,7 @@
         <v>45546</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29188,7 +29195,7 @@
         <v>44830</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29266,7 +29273,7 @@
         <v>44830</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29344,7 +29351,7 @@
         <v>44830</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29422,7 +29429,7 @@
         <v>44830</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29500,7 +29507,7 @@
         <v>44830</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29578,7 +29585,7 @@
         <v>45343</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29651,7 +29658,7 @@
         <v>44776</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29724,7 +29731,7 @@
         <v>44967</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29797,7 +29804,7 @@
         <v>44967</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29870,7 +29877,7 @@
         <v>45205</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29948,7 +29955,7 @@
         <v>45243</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30026,7 +30033,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30099,7 +30106,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30172,7 +30179,7 @@
         <v>44494</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30245,7 +30252,7 @@
         <v>44914</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30318,7 +30325,7 @@
         <v>46243</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30391,7 +30398,7 @@
         <v>45540</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30464,7 +30471,7 @@
         <v>45880</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30542,7 +30549,7 @@
         <v>46288</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30615,7 +30622,7 @@
         <v>45562</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30688,7 +30695,7 @@
         <v>44992</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30761,7 +30768,7 @@
         <v>44637</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30834,7 +30841,7 @@
         <v>44641</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30907,7 +30914,7 @@
         <v>44592</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30980,7 +30987,7 @@
         <v>45401</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31053,7 +31060,7 @@
         <v>46066</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31131,7 +31138,7 @@
         <v>45476</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31209,7 +31216,7 @@
         <v>46290</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31282,7 +31289,7 @@
         <v>45425</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31355,7 +31362,7 @@
         <v>44930</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31428,7 +31435,7 @@
         <v>44487</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31501,7 +31508,7 @@
         <v>44573</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31574,7 +31581,7 @@
         <v>44887</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31647,7 +31654,7 @@
         <v>44931</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31720,7 +31727,7 @@
         <v>44575</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31793,7 +31800,7 @@
         <v>44516</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31866,7 +31873,7 @@
         <v>44742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31939,7 +31946,7 @@
         <v>44613</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32012,7 +32019,7 @@
         <v>45030</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32090,7 +32097,7 @@
         <v>44725</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32163,7 +32170,7 @@
         <v>44566</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32236,7 +32243,7 @@
         <v>45034</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32309,7 +32316,7 @@
         <v>44942</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32382,7 +32389,7 @@
         <v>45659</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32460,7 +32467,7 @@
         <v>44865</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32533,7 +32540,7 @@
         <v>45091</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32606,7 +32613,7 @@
         <v>44830</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32684,7 +32691,7 @@
         <v>45114</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32757,7 +32764,7 @@
         <v>45747</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32830,7 +32837,7 @@
         <v>45294</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32903,7 +32910,7 @@
         <v>44942</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32976,7 +32983,7 @@
         <v>45061</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33049,7 +33056,7 @@
         <v>45603</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33122,7 +33129,7 @@
         <v>44935</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33195,7 +33202,7 @@
         <v>45079</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33268,7 +33275,7 @@
         <v>45279</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33341,7 +33348,7 @@
         <v>44937</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33419,7 +33426,7 @@
         <v>45589</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33492,7 +33499,7 @@
         <v>45460</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33565,7 +33572,7 @@
         <v>45222</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33638,7 +33645,7 @@
         <v>44967</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33711,7 +33718,7 @@
         <v>44967</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33784,7 +33791,7 @@
         <v>44984</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33857,7 +33864,7 @@
         <v>45204</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33935,7 +33942,7 @@
         <v>45266</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34008,7 +34015,7 @@
         <v>45429</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34081,7 +34088,7 @@
         <v>45454</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34154,7 +34161,7 @@
         <v>45215</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34232,7 +34239,7 @@
         <v>45781</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34305,7 +34312,7 @@
         <v>45708</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34378,7 +34385,7 @@
         <v>45615</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34451,7 +34458,7 @@
         <v>45469</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34524,7 +34531,7 @@
         <v>45589</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34597,7 +34604,7 @@
         <v>44903</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34675,7 +34682,7 @@
         <v>45604</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34748,7 +34755,7 @@
         <v>45632</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34821,7 +34828,7 @@
         <v>45222</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34894,7 +34901,7 @@
         <v>45526</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34967,7 +34974,7 @@
         <v>45205</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35045,7 +35052,7 @@
         <v>45474</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35118,7 +35125,7 @@
         <v>45475</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35191,7 +35198,7 @@
         <v>45763</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35269,7 +35276,7 @@
         <v>45786</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35347,7 +35354,7 @@
         <v>45796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35420,7 +35427,7 @@
         <v>46071</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35493,7 +35500,7 @@
         <v>46077</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35566,7 +35573,7 @@
         <v>46104</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45596</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45337</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45884</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17738-2026</t>
+          <t>A 6793-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46122</v>
+        <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,22 +1952,17 @@
           <t>MOTALA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>8.699999999999999</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -1982,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -1997,6 +1992,125 @@
         <v>10</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Ekorrbär
+Liljekonvalj
+Linnea
+Mattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0583/artfynd/A 6793-2022 artfynd.xlsx", "A 6793-2022")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor/A 6793-2022 karta.png", "A 6793-2022")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor_geotiff/A 6793-2022 georefererad karta.tif", "A 6793-2022")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0583/knärot/A 6793-2022 karta knärot.png", "A 6793-2022")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomål/A 6793-2022 FSC-klagomål.docx", "A 6793-2022")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomålsmail/A 6793-2022 FSC-klagomål mail.docx", "A 6793-2022")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsyn/A 6793-2022 tillsynsbegäran.docx", "A 6793-2022")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsynsmail/A 6793-2022 tillsynsbegäran mail.docx", "A 6793-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17738-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MOTALA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gullpudra
@@ -2006,116 +2120,116 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/artfynd/A 17738-2026 artfynd.xlsx", "A 17738-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor/A 17738-2026 karta.png", "A 17738-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor_geotiff/A 17738-2026 georefererad karta.tif", "A 17738-2026")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/knärot/A 17738-2026 karta knärot.png", "A 17738-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomål/A 17738-2026 FSC-klagomål.docx", "A 17738-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomålsmail/A 17738-2026 FSC-klagomål mail.docx", "A 17738-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsyn/A 17738-2026 tillsynsbegäran.docx", "A 17738-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsynsmail/A 17738-2026 tillsynsbegäran mail.docx", "A 17738-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 63217-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MOTALA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MOTALA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>6</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>9</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Gropticka
@@ -2125,116 +2239,116 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/artfynd/A 63217-2025 artfynd.xlsx", "A 63217-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor/A 63217-2025 karta.png", "A 63217-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor_geotiff/A 63217-2025 georefererad karta.tif", "A 63217-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomål/A 63217-2025 FSC-klagomål.docx", "A 63217-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomålsmail/A 63217-2025 FSC-klagomål mail.docx", "A 63217-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsyn/A 63217-2025 tillsynsbegäran.docx", "A 63217-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsynsmail/A 63217-2025 tillsynsbegäran mail.docx", "A 63217-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/fåglar/A 63217-2025 prioriterade fågelarter.docx", "A 63217-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 27273-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>46188</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MOTALA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="E16" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MOTALA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>1.1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>6</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>6</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>6</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Thomsons trägnagare
 Vågbandad barkbock
@@ -2244,111 +2358,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/artfynd/A 27273-2026 artfynd.xlsx", "A 27273-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor/A 27273-2026 karta.png", "A 27273-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor_geotiff/A 27273-2026 georefererad karta.tif", "A 27273-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomål/A 27273-2026 FSC-klagomål.docx", "A 27273-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomålsmail/A 27273-2026 FSC-klagomål mail.docx", "A 27273-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsyn/A 27273-2026 tillsynsbegäran.docx", "A 27273-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsynsmail/A 27273-2026 tillsynsbegäran mail.docx", "A 27273-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/fåglar/A 27273-2026 prioriterade fågelarter.docx", "A 27273-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 28395-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>44747</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MOTALA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MOTALA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>6</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>6</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>6</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Skogsgås
 Nattskärra
@@ -2358,116 +2472,116 @@
 Sångsvan</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/artfynd/A 28395-2022 artfynd.xlsx", "A 28395-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor/A 28395-2022 karta.png", "A 28395-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor_geotiff/A 28395-2022 georefererad karta.tif", "A 28395-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomål/A 28395-2022 FSC-klagomål.docx", "A 28395-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomålsmail/A 28395-2022 FSC-klagomål mail.docx", "A 28395-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsyn/A 28395-2022 tillsynsbegäran.docx", "A 28395-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsynsmail/A 28395-2022 tillsynsbegäran mail.docx", "A 28395-2022")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/fåglar/A 28395-2022 prioriterade fågelarter.docx", "A 28395-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 3721-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>44951</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MOTALA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MOTALA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>4.7</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>8</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Mindre hackspett
@@ -2476,120 +2590,120 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/artfynd/A 3721-2023 artfynd.xlsx", "A 3721-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor/A 3721-2023 karta.png", "A 3721-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor_geotiff/A 3721-2023 georefererad karta.tif", "A 3721-2023")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/knärot/A 3721-2023 karta knärot.png", "A 3721-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomål/A 3721-2023 FSC-klagomål.docx", "A 3721-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomålsmail/A 3721-2023 FSC-klagomål mail.docx", "A 3721-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsyn/A 3721-2023 tillsynsbegäran.docx", "A 3721-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsynsmail/A 3721-2023 tillsynsbegäran mail.docx", "A 3721-2023")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/fåglar/A 3721-2023 prioriterade fågelarter.docx", "A 3721-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>S 2590-2024</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45476</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MOTALA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MOTALA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>4.3</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>3</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>5</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>14</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>13</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Tallticka
@@ -2598,148 +2712,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/artfynd/S 2590-2024 artfynd.xlsx", "S 2590-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor/S 2590-2024 karta.png", "S 2590-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor_geotiff/S 2590-2024 georefererad karta.tif", "S 2590-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomål/S 2590-2024 FSC-klagomål.docx", "S 2590-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomålsmail/S 2590-2024 FSC-klagomål mail.docx", "S 2590-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsyn/S 2590-2024 tillsynsbegäran.docx", "S 2590-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsynsmail/S 2590-2024 tillsynsbegäran mail.docx", "S 2590-2024")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0583/fåglar/S 2590-2024 prioriterade fågelarter.docx", "S 2590-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 6793-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44602</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MOTALA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Linnea
-Mattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0583/artfynd/A 6793-2022 artfynd.xlsx", "A 6793-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor/A 6793-2022 karta.png", "A 6793-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0583/kartor_geotiff/A 6793-2022 georefererad karta.tif", "A 6793-2022")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0583/knärot/A 6793-2022 karta knärot.png", "A 6793-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomål/A 6793-2022 FSC-klagomål.docx", "A 6793-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0583/klagomålsmail/A 6793-2022 FSC-klagomål mail.docx", "A 6793-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsyn/A 6793-2022 tillsynsbegäran.docx", "A 6793-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0583/tillsynsmail/A 6793-2022 tillsynsbegäran mail.docx", "A 6793-2022")</f>
         <v/>
       </c>
     </row>
@@ -2763,7 +2765,7 @@
         <v>46122</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2880,7 +2882,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2995,7 @@
         <v>46080</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3111,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3221,7 +3223,7 @@
         <v>45671</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3337,7 +3339,7 @@
         <v>45531</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3444,7 +3446,7 @@
         <v>46071</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3551,7 +3553,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3657,7 +3659,7 @@
         <v>45958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3763,7 +3765,7 @@
         <v>45103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3878,7 +3880,7 @@
         <v>46141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3986,7 @@
         <v>45918</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4090,7 +4092,7 @@
         <v>46191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4201,7 +4203,7 @@
         <v>45590</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4307,7 +4309,7 @@
         <v>45044</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4413,7 +4415,7 @@
         <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4528,7 +4530,7 @@
         <v>44544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4638,7 +4640,7 @@
         <v>44547</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4748,7 +4750,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4862,7 +4864,7 @@
         <v>44874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4972,7 +4974,7 @@
         <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5077,7 +5079,7 @@
         <v>46122</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5191,7 +5193,7 @@
         <v>46122</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5301,7 +5303,7 @@
         <v>44942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5410,7 +5412,7 @@
         <v>45798</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5517,7 @@
         <v>45918</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5620,7 +5622,7 @@
         <v>46191</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5734,7 +5736,7 @@
         <v>45763</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5844,7 +5846,7 @@
         <v>45068</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5949,7 +5951,7 @@
         <v>45733</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6056,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6159,7 +6161,7 @@
         <v>45602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6266,7 @@
         <v>45390</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6369,7 +6371,7 @@
         <v>44701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6479,7 +6481,7 @@
         <v>45685</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6593,7 +6595,7 @@
         <v>45481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6703,7 +6705,7 @@
         <v>45763</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6815,7 @@
         <v>45804</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6923,7 +6925,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6998,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7069,7 +7071,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7142,7 +7144,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7215,7 +7217,7 @@
         <v>44468</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7288,7 +7290,7 @@
         <v>44586</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7361,7 +7363,7 @@
         <v>44603</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7439,7 +7441,7 @@
         <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7512,7 +7514,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7585,7 +7587,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7663,7 +7665,7 @@
         <v>44741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7736,7 +7738,7 @@
         <v>44628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7814,7 +7816,7 @@
         <v>44692</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7892,7 +7894,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7965,7 +7967,7 @@
         <v>44837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8038,7 +8040,7 @@
         <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8111,7 +8113,7 @@
         <v>44677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8184,7 +8186,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8262,7 +8264,7 @@
         <v>44819</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8335,7 +8337,7 @@
         <v>44860</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8413,7 +8415,7 @@
         <v>44722</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8486,7 +8488,7 @@
         <v>44846</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8559,7 +8561,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8632,7 +8634,7 @@
         <v>44624</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8705,7 +8707,7 @@
         <v>44495</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8778,7 +8780,7 @@
         <v>44518</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8851,7 +8853,7 @@
         <v>44565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8924,7 +8926,7 @@
         <v>44518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8997,7 +8999,7 @@
         <v>44617</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9070,7 +9072,7 @@
         <v>44645</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9143,7 +9145,7 @@
         <v>44830</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9221,7 +9223,7 @@
         <v>44606</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9294,7 +9296,7 @@
         <v>44740</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9367,7 +9369,7 @@
         <v>44573</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9440,7 +9442,7 @@
         <v>44474</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9513,7 +9515,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9586,7 +9588,7 @@
         <v>44809</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9664,7 +9666,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9737,7 +9739,7 @@
         <v>44799</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9810,7 +9812,7 @@
         <v>44834</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9883,7 +9885,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9956,7 +9958,7 @@
         <v>44574</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10029,7 +10031,7 @@
         <v>44525</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10102,7 +10104,7 @@
         <v>44608</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10175,7 +10177,7 @@
         <v>44830</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10253,7 +10255,7 @@
         <v>44749</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10326,7 +10328,7 @@
         <v>44882</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10404,7 +10406,7 @@
         <v>44526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10477,7 +10479,7 @@
         <v>44796</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10555,7 +10557,7 @@
         <v>44528</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10628,7 +10630,7 @@
         <v>44501</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10701,7 +10703,7 @@
         <v>44518</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10774,7 +10776,7 @@
         <v>44496</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10847,7 +10849,7 @@
         <v>44484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10920,7 +10922,7 @@
         <v>44809</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10998,7 +11000,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11076,7 +11078,7 @@
         <v>45215</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11149,7 +11151,7 @@
         <v>45335</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11227,7 +11229,7 @@
         <v>45377</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11300,7 +11302,7 @@
         <v>45378</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11373,7 +11375,7 @@
         <v>44776</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11446,7 +11448,7 @@
         <v>45069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11519,7 +11521,7 @@
         <v>45439</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11592,7 +11594,7 @@
         <v>45440</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11665,7 +11667,7 @@
         <v>44830</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11743,7 +11745,7 @@
         <v>45427</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11816,7 +11818,7 @@
         <v>45302</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11894,7 +11896,7 @@
         <v>45387</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11967,7 +11969,7 @@
         <v>44853</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12045,7 +12047,7 @@
         <v>45666</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12118,7 +12120,7 @@
         <v>45526</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12191,7 +12193,7 @@
         <v>45470</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12269,7 +12271,7 @@
         <v>45279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12342,7 +12344,7 @@
         <v>45279</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12415,7 +12417,7 @@
         <v>44894</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12493,7 +12495,7 @@
         <v>45629</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12566,7 +12568,7 @@
         <v>45092</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12644,7 +12646,7 @@
         <v>45644</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12717,7 +12719,7 @@
         <v>45279</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12790,7 +12792,7 @@
         <v>44942</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12863,7 +12865,7 @@
         <v>45630</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12936,7 +12938,7 @@
         <v>45266</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13009,7 +13011,7 @@
         <v>45266</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13082,7 +13084,7 @@
         <v>45266</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13155,7 +13157,7 @@
         <v>45689</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13228,7 +13230,7 @@
         <v>45547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13301,7 +13303,7 @@
         <v>45798</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13379,7 +13381,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13452,7 +13454,7 @@
         <v>45889</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13525,7 +13527,7 @@
         <v>45898</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13598,7 +13600,7 @@
         <v>45898</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13671,7 +13673,7 @@
         <v>46001</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13744,7 +13746,7 @@
         <v>45575</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13817,7 +13819,7 @@
         <v>44953</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13890,7 +13892,7 @@
         <v>46055</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13963,7 +13965,7 @@
         <v>44539</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14036,7 +14038,7 @@
         <v>46058</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14109,7 +14111,7 @@
         <v>45202</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14182,7 +14184,7 @@
         <v>46061</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14255,7 +14257,7 @@
         <v>45803</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14328,7 +14330,7 @@
         <v>45001</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14401,7 +14403,7 @@
         <v>46064</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14474,7 +14476,7 @@
         <v>46064</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14547,7 +14549,7 @@
         <v>46066</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14625,7 +14627,7 @@
         <v>46066</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14703,7 +14705,7 @@
         <v>46066</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14781,7 +14783,7 @@
         <v>46066</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14859,7 +14861,7 @@
         <v>46066</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14937,7 +14939,7 @@
         <v>46066</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15015,7 +15017,7 @@
         <v>45923</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15088,7 +15090,7 @@
         <v>46069</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15161,7 +15163,7 @@
         <v>46069</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15234,7 +15236,7 @@
         <v>46077</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15307,7 +15309,7 @@
         <v>46073</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15380,7 +15382,7 @@
         <v>45930</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15453,7 +15455,7 @@
         <v>45930</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15526,7 +15528,7 @@
         <v>45930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15599,7 +15601,7 @@
         <v>45930</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15672,7 +15674,7 @@
         <v>45930</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15745,7 +15747,7 @@
         <v>45930</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15818,7 +15820,7 @@
         <v>45930</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15891,7 +15893,7 @@
         <v>45930</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15964,7 +15966,7 @@
         <v>46080</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16037,7 +16039,7 @@
         <v>44931</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16115,7 +16117,7 @@
         <v>45440</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16188,7 +16190,7 @@
         <v>45343</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16261,7 +16263,7 @@
         <v>44907</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16334,7 +16336,7 @@
         <v>46091</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16407,7 +16409,7 @@
         <v>46091</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16480,7 +16482,7 @@
         <v>46091</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16553,7 +16555,7 @@
         <v>45938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16631,7 +16633,7 @@
         <v>45938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16709,7 +16711,7 @@
         <v>45229</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16782,7 +16784,7 @@
         <v>46092</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16855,7 +16857,7 @@
         <v>46092</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16928,7 +16930,7 @@
         <v>46092</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17001,7 +17003,7 @@
         <v>45939</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17079,7 +17081,7 @@
         <v>44951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17157,7 +17159,7 @@
         <v>46094</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17235,7 +17237,7 @@
         <v>46094</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17313,7 +17315,7 @@
         <v>46094</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17391,7 +17393,7 @@
         <v>46094</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17469,7 +17471,7 @@
         <v>44911</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17542,7 +17544,7 @@
         <v>46100</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17620,7 +17622,7 @@
         <v>45946</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17693,7 +17695,7 @@
         <v>44679</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17766,7 +17768,7 @@
         <v>45945</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17839,7 +17841,7 @@
         <v>46104</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17912,7 +17914,7 @@
         <v>46105</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17985,7 +17987,7 @@
         <v>46105</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18058,7 +18060,7 @@
         <v>46106</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18131,7 +18133,7 @@
         <v>45607</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18209,7 +18211,7 @@
         <v>45180</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18282,7 +18284,7 @@
         <v>45964</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18360,7 +18362,7 @@
         <v>46122</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18433,7 +18435,7 @@
         <v>46122</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18511,7 +18513,7 @@
         <v>45964</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18584,7 +18586,7 @@
         <v>45965</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18657,7 +18659,7 @@
         <v>44942</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18730,7 +18732,7 @@
         <v>44952</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18803,7 +18805,7 @@
         <v>45644</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18876,7 +18878,7 @@
         <v>44503</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18949,7 +18951,7 @@
         <v>46132</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19027,7 +19029,7 @@
         <v>46132</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19105,7 +19107,7 @@
         <v>45615</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19178,7 +19180,7 @@
         <v>44999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19256,7 +19258,7 @@
         <v>44819</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19329,7 +19331,7 @@
         <v>45614</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19402,7 +19404,7 @@
         <v>45954</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19480,7 +19482,7 @@
         <v>45099</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19553,7 +19555,7 @@
         <v>45161</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19626,7 +19628,7 @@
         <v>44782</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19699,7 +19701,7 @@
         <v>45695</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19772,7 +19774,7 @@
         <v>45114</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19845,7 +19847,7 @@
         <v>45998</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19918,7 +19920,7 @@
         <v>46003</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19991,7 +19993,7 @@
         <v>46003</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20064,7 +20066,7 @@
         <v>45839</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20137,7 +20139,7 @@
         <v>44819</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20210,7 +20212,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20283,7 +20285,7 @@
         <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20356,7 +20358,7 @@
         <v>44901</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20429,7 +20431,7 @@
         <v>45112</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20502,7 +20504,7 @@
         <v>46141</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20575,7 +20577,7 @@
         <v>46142</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20653,7 +20655,7 @@
         <v>44615</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20726,7 +20728,7 @@
         <v>45043</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20804,7 +20806,7 @@
         <v>45243</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20882,7 +20884,7 @@
         <v>45243</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20960,7 +20962,7 @@
         <v>46142</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21038,7 +21040,7 @@
         <v>45831</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21111,7 +21113,7 @@
         <v>46142</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21189,7 +21191,7 @@
         <v>44881</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21262,7 +21264,7 @@
         <v>44890</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21335,7 +21337,7 @@
         <v>44750</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21408,7 +21410,7 @@
         <v>44879</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21486,7 +21488,7 @@
         <v>45812</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21559,7 +21561,7 @@
         <v>45562</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21632,7 +21634,7 @@
         <v>45279</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21705,7 +21707,7 @@
         <v>46160</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21783,7 +21785,7 @@
         <v>46158</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21856,7 +21858,7 @@
         <v>45484</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21929,7 +21931,7 @@
         <v>46160</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22007,7 +22009,7 @@
         <v>46160</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22085,7 +22087,7 @@
         <v>45183</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22158,7 +22160,7 @@
         <v>46160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22236,7 +22238,7 @@
         <v>45839</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22309,7 +22311,7 @@
         <v>44998</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22387,7 +22389,7 @@
         <v>45817</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22460,7 +22462,7 @@
         <v>45316</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22533,7 +22535,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22606,7 +22608,7 @@
         <v>46163</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22684,7 +22686,7 @@
         <v>45575</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22757,7 +22759,7 @@
         <v>45726</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22830,7 +22832,7 @@
         <v>46167</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22908,7 +22910,7 @@
         <v>45805</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22981,7 +22983,7 @@
         <v>45237</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23054,7 +23056,7 @@
         <v>45329</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23127,7 +23129,7 @@
         <v>44676</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23200,7 +23202,7 @@
         <v>45593</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23278,7 +23280,7 @@
         <v>45798</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23356,7 +23358,7 @@
         <v>44628</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23434,7 +23436,7 @@
         <v>45111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23507,7 +23509,7 @@
         <v>46174</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23585,7 +23587,7 @@
         <v>44865</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23658,7 +23660,7 @@
         <v>46174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23736,7 +23738,7 @@
         <v>45069</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23809,7 +23811,7 @@
         <v>45747</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23882,7 +23884,7 @@
         <v>46174</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23960,7 +23962,7 @@
         <v>45029</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24033,7 +24035,7 @@
         <v>46174</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24111,7 +24113,7 @@
         <v>45428</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24184,7 +24186,7 @@
         <v>44516</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24257,7 +24259,7 @@
         <v>44984</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24330,7 +24332,7 @@
         <v>44987</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24408,7 +24410,7 @@
         <v>46188</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24486,7 +24488,7 @@
         <v>45793</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24564,7 +24566,7 @@
         <v>45173</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24637,7 +24639,7 @@
         <v>45575</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24710,7 +24712,7 @@
         <v>46188</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24788,7 +24790,7 @@
         <v>45602</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24861,7 +24863,7 @@
         <v>46190</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24939,7 +24941,7 @@
         <v>46190</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25017,7 +25019,7 @@
         <v>45343</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25090,7 +25092,7 @@
         <v>45484</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25163,7 +25165,7 @@
         <v>46191</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25241,7 +25243,7 @@
         <v>46190</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25314,7 +25316,7 @@
         <v>44606</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25387,7 +25389,7 @@
         <v>45187</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25460,7 +25462,7 @@
         <v>45377</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25533,7 +25535,7 @@
         <v>45439</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25606,7 +25608,7 @@
         <v>46198</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25684,7 +25686,7 @@
         <v>46198</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25762,7 +25764,7 @@
         <v>46199</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25835,7 +25837,7 @@
         <v>46198</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25913,7 +25915,7 @@
         <v>46198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25991,7 +25993,7 @@
         <v>45473</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26064,7 +26066,7 @@
         <v>45187</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26137,7 +26139,7 @@
         <v>44645</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26210,7 +26212,7 @@
         <v>46202</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26283,7 +26285,7 @@
         <v>46066</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26361,7 +26363,7 @@
         <v>45427</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26434,7 +26436,7 @@
         <v>46204</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26512,7 +26514,7 @@
         <v>45351</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26585,7 +26587,7 @@
         <v>45597</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26663,7 +26665,7 @@
         <v>45624</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26736,7 +26738,7 @@
         <v>45183</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26809,7 +26811,7 @@
         <v>45621</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26887,7 +26889,7 @@
         <v>45224</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26960,7 +26962,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27033,7 +27035,7 @@
         <v>44608</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27106,7 +27108,7 @@
         <v>44608</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27179,7 +27181,7 @@
         <v>45685</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27252,7 +27254,7 @@
         <v>45351</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27325,7 +27327,7 @@
         <v>46255</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27403,7 +27405,7 @@
         <v>46255</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27481,7 +27483,7 @@
         <v>46255</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27559,7 +27561,7 @@
         <v>45099</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27632,7 +27634,7 @@
         <v>46255</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27710,7 +27712,7 @@
         <v>45614</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27783,7 +27785,7 @@
         <v>46259</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27856,7 +27858,7 @@
         <v>44748</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27929,7 +27931,7 @@
         <v>44748</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28002,7 +28004,7 @@
         <v>44725</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28075,7 +28077,7 @@
         <v>45237</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28148,7 +28150,7 @@
         <v>44776</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28221,7 +28223,7 @@
         <v>46218</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28299,7 +28301,7 @@
         <v>46218</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28377,7 +28379,7 @@
         <v>46218</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28455,7 +28457,7 @@
         <v>45187</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28528,7 +28530,7 @@
         <v>45302</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28606,7 +28608,7 @@
         <v>44734</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28679,7 +28681,7 @@
         <v>45266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28752,7 +28754,7 @@
         <v>44804</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28825,7 +28827,7 @@
         <v>44725</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28898,7 +28900,7 @@
         <v>44958</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28971,7 +28973,7 @@
         <v>46273</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29044,7 +29046,7 @@
         <v>45273</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29122,7 +29124,7 @@
         <v>45546</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29195,7 +29197,7 @@
         <v>44830</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29273,7 +29275,7 @@
         <v>44830</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29351,7 +29353,7 @@
         <v>44830</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29429,7 +29431,7 @@
         <v>44830</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29507,7 +29509,7 @@
         <v>44830</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29585,7 +29587,7 @@
         <v>45343</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29658,7 +29660,7 @@
         <v>44776</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29731,7 +29733,7 @@
         <v>44967</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29804,7 +29806,7 @@
         <v>44967</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29877,7 +29879,7 @@
         <v>45205</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29955,7 +29957,7 @@
         <v>45243</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30033,7 +30035,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30106,7 +30108,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30179,7 +30181,7 @@
         <v>44494</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30252,7 +30254,7 @@
         <v>44914</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30325,7 +30327,7 @@
         <v>46243</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30398,7 +30400,7 @@
         <v>45540</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30471,7 +30473,7 @@
         <v>45880</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30549,7 +30551,7 @@
         <v>46288</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30622,7 +30624,7 @@
         <v>45562</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30695,7 +30697,7 @@
         <v>44992</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30768,7 +30770,7 @@
         <v>44637</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30841,7 +30843,7 @@
         <v>44641</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30914,7 +30916,7 @@
         <v>44592</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30987,7 +30989,7 @@
         <v>45401</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31060,7 +31062,7 @@
         <v>46066</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31138,7 +31140,7 @@
         <v>45476</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31216,7 +31218,7 @@
         <v>46290</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31289,7 +31291,7 @@
         <v>45425</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31362,7 +31364,7 @@
         <v>44930</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31435,7 +31437,7 @@
         <v>44487</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31508,7 +31510,7 @@
         <v>44573</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31581,7 +31583,7 @@
         <v>44887</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31654,7 +31656,7 @@
         <v>44931</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31727,7 +31729,7 @@
         <v>44575</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31800,7 +31802,7 @@
         <v>44516</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31873,7 +31875,7 @@
         <v>44742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31946,7 +31948,7 @@
         <v>44613</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32019,7 +32021,7 @@
         <v>45030</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32097,7 +32099,7 @@
         <v>44725</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32170,7 +32172,7 @@
         <v>44566</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32243,7 +32245,7 @@
         <v>45034</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32316,7 +32318,7 @@
         <v>44942</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32389,7 +32391,7 @@
         <v>45659</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32467,7 +32469,7 @@
         <v>44865</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32540,7 +32542,7 @@
         <v>45091</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32613,7 +32615,7 @@
         <v>44830</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32691,7 +32693,7 @@
         <v>45114</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32764,7 +32766,7 @@
         <v>45747</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32837,7 +32839,7 @@
         <v>45294</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32910,7 +32912,7 @@
         <v>44942</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32983,7 +32985,7 @@
         <v>45061</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33056,7 +33058,7 @@
         <v>45603</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33129,7 +33131,7 @@
         <v>44935</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33202,7 +33204,7 @@
         <v>45079</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33275,7 +33277,7 @@
         <v>45279</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33348,7 +33350,7 @@
         <v>44937</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33426,7 +33428,7 @@
         <v>45589</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33499,7 +33501,7 @@
         <v>45460</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33572,7 +33574,7 @@
         <v>45222</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33645,7 +33647,7 @@
         <v>44967</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33718,7 +33720,7 @@
         <v>44967</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33791,7 +33793,7 @@
         <v>44984</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33864,7 +33866,7 @@
         <v>45204</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33942,7 +33944,7 @@
         <v>45266</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34015,7 +34017,7 @@
         <v>45429</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34088,7 +34090,7 @@
         <v>45454</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34161,7 +34163,7 @@
         <v>45215</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34239,7 +34241,7 @@
         <v>45781</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34312,7 +34314,7 @@
         <v>45708</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34385,7 +34387,7 @@
         <v>45615</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34458,7 +34460,7 @@
         <v>45469</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34531,7 +34533,7 @@
         <v>45589</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34604,7 +34606,7 @@
         <v>44903</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34682,7 +34684,7 @@
         <v>45604</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34755,7 +34757,7 @@
         <v>45632</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34828,7 +34830,7 @@
         <v>45222</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34901,7 +34903,7 @@
         <v>45526</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34974,7 +34976,7 @@
         <v>45205</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35052,7 +35054,7 @@
         <v>45474</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35125,7 +35127,7 @@
         <v>45475</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35198,7 +35200,7 @@
         <v>45763</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35276,7 +35278,7 @@
         <v>45786</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35354,7 +35356,7 @@
         <v>45796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35427,7 +35429,7 @@
         <v>46071</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35500,7 +35502,7 @@
         <v>46077</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35573,7 +35575,7 @@
         <v>46104</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45337</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45884</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44747</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>46010</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>46122</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>46188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>45476</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>46122</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>46080</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45531</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>46071</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45918</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45590</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45103</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44547</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45602</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45460</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45390</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>45930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45068</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>46122</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>46122</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45918</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45798</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44942</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>46191</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45685</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44701</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45763</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45804</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44824</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44741</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44692</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44503</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44819</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44722</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44846</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44588</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44624</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44495</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44518</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44617</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44645</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44565</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44518</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44606</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44740</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44573</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44474</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44571</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44809</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>44503</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44799</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44834</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44525</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>44608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44749</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44528</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44796</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44501</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>44518</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44496</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>44484</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>44809</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44830</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44984</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45187</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45387</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44615</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45747</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45001</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45454</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45183</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45279</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45114</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44606</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44903</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>45469</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45589</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>45604</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45343</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45597</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46003</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45998</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>46003</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44566</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45302</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45222</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44992</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44734</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44748</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44952</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45215</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44935</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45173</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45666</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45547</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45644</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45630</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45689</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45798</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46001</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45803</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45644</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>46055</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45923</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>44750</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45540</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46058</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45440</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45930</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45930</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45930</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45930</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45930</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45930</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45930</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>46061</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45111</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>46064</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46064</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45546</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46066</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>46066</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46066</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>46069</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>46069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45939</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45938</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45429</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>46073</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45279</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45946</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>46077</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45202</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>46080</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44575</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44967</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44967</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>45401</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>46091</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>46091</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44776</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>46092</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>46092</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45964</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>46092</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>46094</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>46094</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45965</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45964</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>46094</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>46094</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44942</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>44935</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44865</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44890</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>46104</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46100</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>46106</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>46105</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45470</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>46105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44914</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45237</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>44830</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44645</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>44830</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>44830</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44830</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45343</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45187</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>44628</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44487</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>46122</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>46122</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45112</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44967</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44967</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44901</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44865</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44911</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>46132</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45831</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>46132</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44887</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44931</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45099</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45335</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45069</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45439</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45215</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45215</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45839</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>44592</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45575</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>44881</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45316</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45575</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45726</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45621</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45695</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45659</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45279</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45954</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45593</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>44776</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44951</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45351</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45805</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45114</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45460</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45798</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>45839</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45069</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>45615</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         <v>45092</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45243</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45747</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45484</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>44539</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44748</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44942</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45425</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44725</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45603</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46141</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45427</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>46142</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44958</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45099</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>46142</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>46142</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45575</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45624</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44516</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45812</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45484</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>46158</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>46160</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>46160</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>46160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>46160</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45205</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>46163</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>44676</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>44613</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46167</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>45294</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45029</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45614</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45589</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>46174</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>46174</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>46174</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>46174</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45266</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45602</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45614</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45266</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45266</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45266</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45224</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>44984</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45428</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>45562</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44942</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44853</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>46188</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45279</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45279</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>46188</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>44942</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>46190</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>46190</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45793</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>46190</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>46191</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>44819</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>46198</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>46198</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46198</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>46198</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45439</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45187</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>46202</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>46199</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45562</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44503</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45034</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>46066</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>44830</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>46204</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>46206</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45061</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45183</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45526</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>46218</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>46218</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45351</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>46218</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>45473</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45302</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>46259</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45043</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45427</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45440</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44637</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44998</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45685</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44608</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44608</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>46273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45378</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44725</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>44987</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>46281</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>45377</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45607</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45377</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>44742</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45880</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45243</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>46243</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45243</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45273</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>44804</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>46288</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45237</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44516</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44782</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>44573</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>46290</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>46066</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44999</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45180</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>44894</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45476</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44893</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>46255</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46255</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45030</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>46255</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>46255</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44589</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44641</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>44494</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45266</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44679</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44776</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45229</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45204</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>45222</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>44725</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44819</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44830</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44830</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45329</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44931</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>45343</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45091</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>44907</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45615</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45781</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45708</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45632</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45526</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45205</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45475</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45763</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>45786</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45796</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>46071</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>46077</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>46104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46239</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45337</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45884</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44747</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>46010</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>46122</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>46188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>45476</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>46122</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>46080</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45531</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>46071</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45918</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45590</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45103</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44547</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45602</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45460</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45390</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>45930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45068</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>46122</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>46122</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45918</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45798</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44942</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>46191</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45685</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44701</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45763</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45804</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44824</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44741</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44692</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44503</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>44830</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44819</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44722</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44846</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44588</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44624</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44495</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44518</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44617</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44645</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44565</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44518</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44606</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44740</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44573</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44474</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44571</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44809</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>44503</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44799</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44834</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44525</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>44608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44749</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44528</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44796</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44501</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>44518</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44496</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>44484</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>44809</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44830</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44984</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45187</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45387</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44615</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45747</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45001</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45454</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45183</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45279</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45114</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44606</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44903</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>45469</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45589</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>45604</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45343</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45597</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46003</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45998</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>46003</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44566</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45302</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45222</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44992</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45889</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44734</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44748</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44952</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45215</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44935</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45173</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45666</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45547</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45644</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45630</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45689</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45798</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46001</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45803</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45644</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>46055</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45923</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>44750</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45540</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46058</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45440</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45930</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45930</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45930</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45930</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45930</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45930</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45930</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>46061</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45111</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>46064</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46064</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45546</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46066</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>46066</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>46066</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46066</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>46069</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>46069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45939</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45938</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45429</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>46073</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45279</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45946</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>46077</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45202</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>46080</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44575</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44967</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44967</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>45401</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>46091</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>46091</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44776</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>46092</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>46092</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45964</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>46092</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>46094</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>46094</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45965</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45964</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>46094</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>46094</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44942</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>44935</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44865</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44890</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>46104</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46100</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>46106</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>46105</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45470</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>46105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44914</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45237</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>44830</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44645</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>44830</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>44830</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44830</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45343</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45187</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>44628</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44487</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>46122</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>46122</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45112</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44967</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44967</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44901</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44865</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44911</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>46132</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45831</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>46132</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44887</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44931</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45099</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45335</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45069</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45439</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45215</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45215</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45839</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>44592</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45575</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>44881</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45316</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45575</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45726</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45621</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45695</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45659</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45279</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45954</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45593</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>44776</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44951</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45351</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45805</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45114</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45460</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45798</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>45839</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45069</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>45615</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         <v>45092</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45243</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45747</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45484</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>44539</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44748</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44942</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45425</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44725</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45603</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46141</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45427</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>46142</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44958</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45099</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>46142</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>46142</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45575</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45624</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44516</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45812</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45484</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>46158</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>46160</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>46160</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>46160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>46160</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45205</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>46163</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>44676</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>44613</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46167</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>45294</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45029</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45614</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45589</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>46174</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>46174</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>46174</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>46174</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45266</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45602</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45614</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45266</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45266</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45266</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45224</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>44984</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45428</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>45562</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44942</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44853</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>46188</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45279</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45279</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>46188</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>44942</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>46190</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>46190</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45793</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>46190</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>46191</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>44819</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>46198</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>46198</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46198</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>46198</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45439</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45187</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>46202</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>46199</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45562</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44503</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45034</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>46066</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>44830</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>46204</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>46206</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45061</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45183</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45526</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>46218</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>46218</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45351</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>46218</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>45473</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45302</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>46259</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45043</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45427</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45440</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44637</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44998</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45685</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44608</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44608</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>46273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45378</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44725</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>44987</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>46281</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>45377</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45607</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45377</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>44742</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45880</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45243</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>46243</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45243</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45273</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>44804</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>46288</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45237</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44516</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44782</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>44573</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>46290</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>46066</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44999</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45180</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>44894</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45476</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44893</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>46255</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46255</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45030</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>46255</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>46255</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44589</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44641</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>44494</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45266</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44679</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44776</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45229</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45204</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>45222</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>44725</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>44819</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44830</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44830</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45329</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44931</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>45343</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45091</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>44907</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45615</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45781</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45708</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45632</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45526</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45205</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45475</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45763</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>45786</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45796</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>46071</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>46077</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>46104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45596</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>45897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46239</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>45337</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45884</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44747</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>46122</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>46010</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>46188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>45476</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>46122</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45671</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>46080</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45531</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>46071</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45590</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>45103</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46141</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>46191</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44544</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44547</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>44874</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45390</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45930</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44942</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45763</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>46122</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>46122</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45798</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>45918</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45068</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>46191</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>45685</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45763</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45804</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44824</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44692</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44837</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>44860</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44677</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44819</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44722</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44846</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44588</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44624</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44495</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44518</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44518</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44565</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44617</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44645</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44571</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44830</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>44809</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>44749</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>44496</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44834</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44574</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44574</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44799</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44740</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44573</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44528</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>44525</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44484</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45659</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44809</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44865</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45091</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44881</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45439</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45440</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>44890</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>44830</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>44750</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45377</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>45562</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44830</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45114</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45183</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45215</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45378</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45427</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45302</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44776</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44998</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45294</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45387</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44853</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44893</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44942</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45069</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45061</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45526</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45603</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44935</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45237</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45079</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45470</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45279</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45279</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45279</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44894</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>45329</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44676</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45092</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45593</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44628</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45279</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44942</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45266</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45266</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>45266</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45589</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>45460</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45222</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45889</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44865</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45069</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44967</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>44967</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45898</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44984</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45204</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45266</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45429</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45029</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45428</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>44516</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45454</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45215</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44984</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45781</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45708</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>44953</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45615</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>45469</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44539</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44987</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45589</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>44903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>45202</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45173</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45602</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45001</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45604</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>45343</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45923</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45484</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45632</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44606</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45187</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45222</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45930</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>45930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>45666</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45930</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45930</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45930</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45930</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45629</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>45377</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>45439</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>45644</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45630</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44931</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45689</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45440</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45473</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45547</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45798</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45187</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>44645</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45343</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44907</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45229</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44951</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45427</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45803</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45351</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45597</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45624</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45938</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45183</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45938</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>44911</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45621</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44679</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45224</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>44608</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44608</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45939</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45946</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45685</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45945</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45351</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45180</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45099</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45614</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>44901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45112</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>44942</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>44952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45831</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>44748</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>44748</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44725</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45237</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45644</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44776</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44503</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45839</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45964</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45615</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45187</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44999</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45302</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44819</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45817</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>45316</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45614</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45099</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44734</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>45575</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45726</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44782</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45805</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45798</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45266</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45747</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44804</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44725</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>44958</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45575</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44819</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45273</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>44935</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45546</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44830</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44830</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44830</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44830</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>44830</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>46094</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45215</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>45343</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44776</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>46100</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>44967</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>44967</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>46104</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>46105</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45205</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44615</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>46105</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45043</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>45243</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>46106</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44494</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>45243</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45243</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>44914</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>46122</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>46122</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45998</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45540</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>46132</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45562</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>46132</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44992</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44637</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>44641</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44592</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>46003</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>46003</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45401</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45954</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45476</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45425</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>44930</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>44487</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45695</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>44573</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>44887</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>44931</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>44575</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28332,7 +28332,7 @@
         <v>44516</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>46034</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45839</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44742</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>44613</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45030</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>44725</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44566</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45034</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>44942</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>46001</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>46141</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46142</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>46055</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>46058</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>46142</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>46061</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>46142</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>46064</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>46064</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>46066</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>46066</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>46066</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>46066</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>46069</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>46069</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>46077</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>46073</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>46080</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45812</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>46160</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>46158</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45484</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>46160</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46160</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46160</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46091</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>46091</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46092</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46092</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46092</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46094</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46094</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46094</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>46163</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>46167</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>46174</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>46174</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>46174</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46174</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>46188</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>45793</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>46188</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>46190</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32399,7 +32399,7 @@
         <v>46190</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>46191</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>46190</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>46198</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>46198</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>46199</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>46198</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>46198</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>46202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46066</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>46204</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46206</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>46218</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>46218</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>46218</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>46273</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>46281</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>46281</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>46243</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45880</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>46288</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>46066</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>46290</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>46255</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>46300</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>44589</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>46255</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>46255</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>46255</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>46259</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45526</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45205</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45475</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45763</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>45786</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45796</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>46071</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>46077</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>46104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>46239</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45337</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45884</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>46010</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>46188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45476</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>46122</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>46080</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46071</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46141</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46036</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45590</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>46191</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45103</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>44544</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44547</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45798</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>46191</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45763</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>46122</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>46122</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44874</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45918</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45733</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45460</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45390</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45685</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44701</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>45481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45804</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44518</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44881</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44586</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44603</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>44628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>44692</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44837</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44819</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44860</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44722</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44846</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44624</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44495</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44518</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44617</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44645</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44830</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>44606</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>44740</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44573</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>44571</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44809</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44503</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44834</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44799</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44525</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>44608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44749</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44796</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44528</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44501</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44518</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44496</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44809</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44830</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44984</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45187</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44953</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45387</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44615</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44879</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45454</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45747</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45279</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45183</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>44606</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45114</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45597</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44566</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45343</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45302</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>44992</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44734</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45215</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44748</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44935</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44952</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45173</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>44937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45644</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>44750</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45440</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45540</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45111</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45546</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>45279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45429</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44575</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>45202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>44967</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44967</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45401</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44776</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>44942</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44935</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>44865</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44890</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45470</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44914</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44645</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45237</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44830</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>44830</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44830</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44830</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45343</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45187</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45695</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44628</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45954</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>44487</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44967</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44967</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44865</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>44911</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44887</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>44931</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45839</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45335</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45069</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45898</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45898</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45439</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>45215</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45215</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44592</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45575</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>46142</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>46142</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44881</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45923</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45621</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45659</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45593</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45930</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45930</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45930</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44776</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45930</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45930</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44951</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45351</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45114</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45938</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45460</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45945</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45069</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45615</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45092</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45243</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45484</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>44539</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45484</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44748</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44942</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45425</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>46158</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>46160</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44725</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45964</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45603</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45964</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45427</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>44958</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>46160</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>46160</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>46160</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>46163</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45624</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>44516</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>46167</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45205</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44676</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44613</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45294</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46003</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45998</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>46003</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45029</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45589</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46174</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>46174</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>46174</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>46174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45602</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45614</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45266</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45224</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>44984</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45428</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45562</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44942</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>44853</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45279</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45279</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>46034</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44942</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44819</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>46001</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>46055</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>46058</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45439</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>45187</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>46061</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>46064</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>46064</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>46188</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>46066</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>46066</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>46066</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>46066</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>46069</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>46069</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45562</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44503</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45034</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>46073</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>46188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44830</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>46077</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>46080</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>46190</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45061</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>46190</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45793</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>46091</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>46091</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>46092</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>46190</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>46191</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>46092</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>46094</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>46094</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>46094</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45183</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45526</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46104</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45351</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46100</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45473</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>46106</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46105</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45302</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46105</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45043</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>46198</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46198</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>46198</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45427</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45440</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44637</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44998</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45685</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>46122</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44608</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>44608</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46202</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>46199</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>46132</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>46132</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>46066</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45378</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>46204</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44725</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44987</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45377</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45377</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>46206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44742</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45243</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45243</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45273</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>46218</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>46218</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>46218</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44804</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45237</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>44516</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44782</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>44573</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44999</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45180</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>46281</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>44894</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45476</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>44893</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45030</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45880</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>44641</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44494</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>44930</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>46243</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45266</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44679</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>44776</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45229</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46288</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45204</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45222</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44725</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>44819</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44830</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46290</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46066</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>44830</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45329</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>44931</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45343</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45091</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44907</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44589</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>46255</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>46259</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>46255</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45615</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45781</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>46300</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45708</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45632</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>46255</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>46255</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44903</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45469</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45589</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45604</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45222</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46307</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>46307</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45666</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45547</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45629</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45644</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45630</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45689</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45798</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45803</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45112</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44901</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45831</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45839</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45817</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45316</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45575</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>45726</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45805</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45798</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45747</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45575</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45526</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45205</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45475</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45763</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45786</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45796</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46071</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>46077</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>46239</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45337</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45884</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>46010</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>46188</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45476</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>46122</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45671</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>46080</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46071</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46141</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46036</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45590</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>46191</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45103</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>44544</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44547</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45798</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>46191</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45763</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>46122</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>46122</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44874</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45918</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45733</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>45602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45460</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45390</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45685</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44701</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>45481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45804</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44518</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44881</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44586</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44603</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44725</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>44628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>44692</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44837</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44819</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44860</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44722</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44846</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44624</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44495</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44518</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44617</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44645</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44830</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>44606</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>44740</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44573</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>44571</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44809</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44503</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44834</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44799</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44525</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>44608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44749</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44796</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44528</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44501</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44518</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44496</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44809</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44830</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44984</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45187</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44953</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45387</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44615</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44879</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45454</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45747</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45279</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45183</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>44606</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45114</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45597</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44566</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45343</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45302</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>44992</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44734</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45215</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44748</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44935</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44952</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45173</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>44937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45644</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>44750</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45440</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45540</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45111</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45546</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>45279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45429</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44575</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>45202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>44967</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44967</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45401</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44776</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>44942</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44935</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>44865</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44890</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45470</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44914</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44645</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45237</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44830</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>44830</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44830</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44830</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45343</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45187</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45695</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44628</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45954</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>44487</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44967</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44967</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44865</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>44911</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44887</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>44931</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45839</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45335</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45069</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45898</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45898</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45439</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>45215</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45215</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44592</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45575</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>46142</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>46142</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44881</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45923</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45621</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45659</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45593</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45930</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45930</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45930</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44776</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45930</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45930</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44951</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45351</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45114</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45938</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45460</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45945</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45069</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45615</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45092</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45243</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45484</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>44539</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45484</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44748</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>44942</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45425</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>46158</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>46160</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44725</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45964</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45603</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45964</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45427</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>44958</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>46160</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>46160</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>46160</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>46163</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45624</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>44516</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>46167</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45205</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44676</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44613</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45294</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46003</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45998</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>46003</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45029</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45589</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46174</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>46174</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>46174</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>46174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45602</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45614</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45266</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45224</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>44984</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45428</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45562</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44942</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>44853</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45279</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45279</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>46034</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44942</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44819</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>46001</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>46055</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>46058</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45439</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>45187</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>46061</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>46064</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>46064</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>46188</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>46066</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>46066</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>46066</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>46066</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>46069</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>46069</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45562</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44503</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45034</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>46073</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>46188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44830</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>46077</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>46080</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>46190</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45061</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>46190</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45793</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>46091</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>46091</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>46092</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>46190</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>46191</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>46092</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>46094</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>46094</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>46094</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45183</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45526</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46104</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45351</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46100</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45473</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>46106</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46105</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45302</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46105</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45043</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>46198</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46198</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>46198</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45427</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45440</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44637</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44998</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45685</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>46122</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44608</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>44608</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46202</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>46199</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>46132</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>46132</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>46066</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45378</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>46204</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44725</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44987</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45377</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45377</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>46206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44742</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45243</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45243</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45273</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>46218</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>46218</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>46218</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44804</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45237</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>44516</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44782</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>44573</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44999</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45180</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>46281</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>44894</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45476</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>44893</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45030</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45880</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>44641</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44494</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>44930</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>46243</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45266</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44679</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>44776</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45229</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46288</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45204</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45222</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44725</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>44819</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44830</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46290</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46066</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>44830</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45329</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>44931</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45343</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45091</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44907</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44589</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>46255</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>46259</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>46255</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45615</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45781</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>46300</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45708</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45632</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>46255</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>46255</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44903</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45469</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45589</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45604</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45222</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46307</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>46307</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45666</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45547</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45629</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45644</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45630</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45689</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45798</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45803</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45112</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44901</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45831</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45839</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45817</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45316</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45575</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>45726</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45805</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45798</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45747</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45575</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45526</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45205</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45475</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45763</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45786</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45796</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46071</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>46077</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46273</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45596</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45337</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45884</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>46188</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>46010</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45476</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>46122</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>46071</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46080</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45671</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45531</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>46191</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>46141</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>45103</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45590</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>44544</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44547</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>46191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45733</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45602</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45390</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46122</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>46122</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45798</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>45918</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>44874</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44942</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45763</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44701</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45685</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>45481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45804</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>44824</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44692</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44837</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44819</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44722</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44846</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44495</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44518</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44518</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44645</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44606</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44740</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44573</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44571</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44809</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>44503</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44834</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44574</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44525</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44608</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44830</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44749</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44882</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44526</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>44528</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44796</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>44501</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44518</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44592</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44809</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>44830</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45377</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45401</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45215</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45335</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45378</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44776</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45898</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45069</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>45476</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45425</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45898</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>44930</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44931</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>44575</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44516</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>46163</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44742</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45923</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>46167</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44613</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45030</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44725</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44566</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45930</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45930</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45034</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45930</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45930</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45930</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45930</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45930</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45930</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44942</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>46174</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45439</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45440</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>44830</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45938</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45938</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>46174</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45939</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>46174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45659</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>46174</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44865</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45091</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45427</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45302</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45946</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45387</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>44853</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45945</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44830</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45114</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45747</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45294</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>46188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45793</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>46188</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45964</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44942</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>46190</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46190</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>46191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>46190</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45061</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>45603</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>44935</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45079</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46198</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46198</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46199</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>46198</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>46198</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45279</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46202</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>46066</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45589</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45460</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45222</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>46204</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44967</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>44967</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>44984</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45204</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45526</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>46206</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45266</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45429</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45470</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45279</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45279</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>46218</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>46218</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>46218</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45454</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45215</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45998</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>45781</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45708</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>46003</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>46003</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45615</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45469</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45589</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44903</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>46281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>45604</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>46281</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45632</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44894</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45222</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>46034</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45666</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46243</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45629</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>45092</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45644</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45630</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45880</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45689</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45547</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45798</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>46288</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>46001</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45803</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>46055</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>46290</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45279</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>46058</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>46061</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>44942</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46064</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>46064</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>46066</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>46066</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>46066</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>46066</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>46069</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46069</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>46077</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45266</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46073</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44901</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45112</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>46080</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>46091</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>46091</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>46092</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>46092</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45839</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>46092</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>46255</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>46094</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>46094</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>46094</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46300</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>44589</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>46255</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>46255</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>46255</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45817</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45316</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>46100</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>46104</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>46105</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>45575</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>46105</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45726</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>46106</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>46259</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45805</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45798</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45747</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>46122</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45575</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>46132</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46132</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>46307</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46307</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45575</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44953</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45954</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44539</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45695</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45001</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>46315</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>46315</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>46315</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44931</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46141</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45440</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>46142</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45343</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44907</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45229</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46142</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>46318</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44951</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44911</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44679</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45812</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45180</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>46160</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>46158</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45484</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46160</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>46160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>46160</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44942</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45644</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44503</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45615</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44999</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>44819</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45614</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45099</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45161</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44782</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>45114</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>44819</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44935</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45215</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>44615</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45043</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>45243</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45243</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>44881</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>44890</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44750</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44879</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45562</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45279</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45183</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44998</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44893</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>45237</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45329</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>44676</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45593</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>44628</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45111</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44865</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45069</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45428</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>44516</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>44984</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>44987</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45173</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45602</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45343</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45484</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44606</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45187</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45377</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45439</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45473</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>45187</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>44645</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45427</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45351</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45597</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45624</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45183</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45621</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45224</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>44608</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>44608</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45685</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45351</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45099</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45614</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>44748</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44748</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44725</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45237</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44776</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45187</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45302</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44734</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45266</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>44804</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>44725</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44958</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45273</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45546</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>44830</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44830</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>44830</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44830</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44830</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45343</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44776</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44967</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44967</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45205</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45243</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>44494</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>44914</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45540</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45562</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44992</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>44637</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44641</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45526</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45205</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45474</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45763</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45786</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45796</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>46071</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46077</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46104</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>

--- a/Översikt MOTALA.xlsx
+++ b/Översikt MOTALA.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44763</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46239</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46273</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45596</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45337</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45884</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44747</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>46188</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>46010</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>45476</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>46122</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>46071</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46080</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45671</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45531</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>46191</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>46141</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>45103</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45590</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>44544</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44547</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>46191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45733</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>45602</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45390</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46122</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>46122</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45798</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>45918</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>44874</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44942</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45763</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44701</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45685</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>45481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45804</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44572</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>44824</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>44692</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44837</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44819</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44722</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44846</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44495</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44518</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44518</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44645</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44606</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44740</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44573</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44571</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44809</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>44503</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44834</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44574</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44525</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44608</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44830</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44749</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44882</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44526</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>44528</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44796</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>44501</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44518</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44592</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44809</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>44830</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45377</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45401</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45215</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45335</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45378</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44776</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45898</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45069</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>45476</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45425</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45898</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>44930</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44931</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>44575</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44516</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>46163</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44742</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45923</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>46167</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44613</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45030</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44725</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44566</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45930</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45930</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45034</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45930</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45930</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45930</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45930</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45930</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45930</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44942</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>46174</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45439</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45440</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>44830</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45938</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45938</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>46174</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45939</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>46174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45659</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>46174</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44865</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45091</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45427</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45302</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45946</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45387</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>44853</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45945</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44830</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45114</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45747</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45294</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>46188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45793</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>46188</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45964</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44942</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>46190</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46190</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>46191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>46190</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45061</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>45603</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>44935</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45079</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46198</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46198</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46199</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>46198</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>46198</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45279</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46202</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>46066</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45589</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45460</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45222</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>46204</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44967</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>44967</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>44984</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45204</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45526</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>46206</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45266</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45429</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45470</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45279</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45279</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>46218</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>46218</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>46218</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45454</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45215</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45998</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>45781</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45708</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>46003</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>46003</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45615</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45469</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45589</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44903</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>46281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>45604</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>46281</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45632</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44894</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45222</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>46034</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45666</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46243</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45629</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>45092</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45644</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45630</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45880</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45689</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45547</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45798</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>46288</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>46001</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45803</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>46055</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>46290</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45279</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>46058</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>46061</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>44942</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46064</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>46064</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>46066</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>46066</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>46066</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>46066</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>46069</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46069</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>46077</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45266</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46073</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44901</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45112</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>46080</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>46091</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>46091</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>46092</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>46092</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45839</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>46092</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>46255</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>46094</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>46094</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>46094</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46300</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>44589</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>46255</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>46255</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>46255</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45817</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45316</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>46100</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>46104</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>46105</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>45575</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>46105</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45726</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>46106</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>46259</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45805</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45798</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45747</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>46122</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45575</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>46132</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46132</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>46307</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46307</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45575</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44953</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45954</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44539</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45695</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45001</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>46315</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>46315</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>46315</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44931</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46141</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45440</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>46142</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45343</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44907</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45229</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46142</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>46318</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44951</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44911</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44679</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45812</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45180</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>46160</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>46158</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45484</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46160</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>46160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>46160</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44942</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45644</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44503</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45615</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44999</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>44819</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45614</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45099</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45161</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44782</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>45114</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>44819</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44935</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45215</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>44615</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45043</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>45243</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45243</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>44881</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>44890</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44750</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44879</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45562</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45279</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45183</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44998</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44893</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>45237</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45329</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>44676</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45593</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>44628</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45111</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44865</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45069</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45428</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>44516</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>44984</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>44987</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45173</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45602</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45343</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45484</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44606</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45187</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45377</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45439</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45473</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>45187</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>44645</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45427</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45351</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45597</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45624</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45183</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45621</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45224</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>44608</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>44608</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45685</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45351</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45099</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45614</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>44748</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44748</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44725</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45237</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44776</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45187</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45302</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44734</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45266</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>44804</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>44725</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44958</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45273</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45546</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>44830</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44830</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>44830</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44830</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44830</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45343</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44776</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44967</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44967</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45205</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45243</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>44494</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>44914</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45540</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45562</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44992</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>44637</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44641</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45526</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45205</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45474</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45763</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45786</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45796</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>46071</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46077</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46104</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
